--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L755"/>
+  <dimension ref="A1:L759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32156,6 +32156,174 @@
         <v>360.6</v>
       </c>
       <c r="L755" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="C756" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="D756" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="E756" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="F756" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="G756" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="H756" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="I756" t="n">
+        <v>338.29</v>
+      </c>
+      <c r="J756" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="K756" t="n">
+        <v>360.03</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>329.18</v>
+      </c>
+      <c r="C757" t="n">
+        <v>329.31</v>
+      </c>
+      <c r="D757" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="E757" t="n">
+        <v>353.56</v>
+      </c>
+      <c r="F757" t="n">
+        <v>347.8</v>
+      </c>
+      <c r="G757" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="H757" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="I757" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="J757" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="K757" t="n">
+        <v>359.86</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="C758" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="D758" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="E758" t="n">
+        <v>353.48</v>
+      </c>
+      <c r="F758" t="n">
+        <v>347.56</v>
+      </c>
+      <c r="G758" t="n">
+        <v>339.48</v>
+      </c>
+      <c r="H758" t="n">
+        <v>329.26</v>
+      </c>
+      <c r="I758" t="n">
+        <v>338.92</v>
+      </c>
+      <c r="J758" t="n">
+        <v>352.93</v>
+      </c>
+      <c r="K758" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>329.65</v>
+      </c>
+      <c r="C759" t="n">
+        <v>329.66</v>
+      </c>
+      <c r="D759" t="n">
+        <v>335.45</v>
+      </c>
+      <c r="E759" t="n">
+        <v>353.17</v>
+      </c>
+      <c r="F759" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="G759" t="n">
+        <v>339.64</v>
+      </c>
+      <c r="H759" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="I759" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="J759" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="K759" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="L759" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32172,7 +32340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B760"/>
+  <dimension ref="A1:B764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39775,6 +39943,46 @@
       </c>
       <c r="B760" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -39943,28 +40151,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.439007986401406</v>
+        <v>-0.4401836375475784</v>
       </c>
       <c r="J2" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K2" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1227949045490682</v>
+        <v>0.1246937783485814</v>
       </c>
       <c r="M2" t="n">
-        <v>7.155395226707337</v>
+        <v>7.123572498176651</v>
       </c>
       <c r="N2" t="n">
-        <v>75.31704687597419</v>
+        <v>74.92602105369974</v>
       </c>
       <c r="O2" t="n">
-        <v>8.678539443706768</v>
+        <v>8.655981807611413</v>
       </c>
       <c r="P2" t="n">
-        <v>342.4239454632108</v>
+        <v>342.436637966387</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -40021,28 +40229,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1951018715542421</v>
+        <v>-0.1985965081224934</v>
       </c>
       <c r="J3" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K3" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09727323581817848</v>
+        <v>0.1012893096785074</v>
       </c>
       <c r="M3" t="n">
-        <v>3.683759831379467</v>
+        <v>3.682053402299097</v>
       </c>
       <c r="N3" t="n">
-        <v>19.32473148367772</v>
+        <v>19.27743120873906</v>
       </c>
       <c r="O3" t="n">
-        <v>4.395990387122988</v>
+        <v>4.390607157186698</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0175329279596</v>
+        <v>338.0552607223181</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -40099,28 +40307,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.146455363829572</v>
+        <v>-0.1486592826059505</v>
       </c>
       <c r="J4" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K4" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0307002110247836</v>
+        <v>0.03195936985671766</v>
       </c>
       <c r="M4" t="n">
-        <v>5.038917365868932</v>
+        <v>5.023673525044476</v>
       </c>
       <c r="N4" t="n">
-        <v>37.0471635938075</v>
+        <v>36.87475068046071</v>
       </c>
       <c r="O4" t="n">
-        <v>6.086638119176094</v>
+        <v>6.072458372064869</v>
       </c>
       <c r="P4" t="n">
-        <v>341.9546353315924</v>
+        <v>341.9784321436476</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40177,28 +40385,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04879707336245043</v>
+        <v>-0.05023217489140925</v>
       </c>
       <c r="J5" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K5" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006655456051401942</v>
+        <v>0.007132501544959813</v>
       </c>
       <c r="M5" t="n">
-        <v>3.456357307860996</v>
+        <v>3.444857454639962</v>
       </c>
       <c r="N5" t="n">
-        <v>19.44183637080527</v>
+        <v>19.34920088170597</v>
       </c>
       <c r="O5" t="n">
-        <v>4.409289780770285</v>
+        <v>4.398772656287885</v>
       </c>
       <c r="P5" t="n">
-        <v>356.2511012274655</v>
+        <v>356.266597113566</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40255,28 +40463,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1945891586947628</v>
+        <v>-0.1912012230144396</v>
       </c>
       <c r="J6" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K6" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06454516762294193</v>
+        <v>0.06307458373127206</v>
       </c>
       <c r="M6" t="n">
-        <v>4.335199015899225</v>
+        <v>4.331505688486628</v>
       </c>
       <c r="N6" t="n">
-        <v>30.02092103389892</v>
+        <v>29.91449036743143</v>
       </c>
       <c r="O6" t="n">
-        <v>5.479135062571365</v>
+        <v>5.469414078987934</v>
       </c>
       <c r="P6" t="n">
-        <v>349.9508746016546</v>
+        <v>349.9143005269853</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40333,28 +40541,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2633744070052741</v>
+        <v>-0.2604644320167772</v>
       </c>
       <c r="J7" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K7" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1119927889991305</v>
+        <v>0.1108787485879021</v>
       </c>
       <c r="M7" t="n">
-        <v>4.27811666795616</v>
+        <v>4.269984226893748</v>
       </c>
       <c r="N7" t="n">
-        <v>30.08854696995111</v>
+        <v>29.96809775132403</v>
       </c>
       <c r="O7" t="n">
-        <v>5.485302814790731</v>
+        <v>5.474312536869267</v>
       </c>
       <c r="P7" t="n">
-        <v>344.2031946875757</v>
+        <v>344.1717801723373</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40411,28 +40619,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.137958068383621</v>
+        <v>-0.1464670536011987</v>
       </c>
       <c r="J8" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K8" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03783975488709912</v>
+        <v>0.04244779846559743</v>
       </c>
       <c r="M8" t="n">
-        <v>4.032100674518665</v>
+        <v>4.046810934445029</v>
       </c>
       <c r="N8" t="n">
-        <v>26.47408418585983</v>
+        <v>26.65856868098542</v>
       </c>
       <c r="O8" t="n">
-        <v>5.145297288384786</v>
+        <v>5.163193651315571</v>
       </c>
       <c r="P8" t="n">
-        <v>341.0220056870387</v>
+        <v>341.1138693652686</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40489,28 +40697,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02801752302243645</v>
+        <v>0.02148138318597408</v>
       </c>
       <c r="J9" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K9" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002072574222526935</v>
+        <v>0.001223046209241185</v>
       </c>
       <c r="M9" t="n">
-        <v>3.484235574239093</v>
+        <v>3.488461957397977</v>
       </c>
       <c r="N9" t="n">
-        <v>20.67645033243967</v>
+        <v>20.75868220875254</v>
       </c>
       <c r="O9" t="n">
-        <v>4.547136498109515</v>
+        <v>4.5561696861237</v>
       </c>
       <c r="P9" t="n">
-        <v>343.9559011415</v>
+        <v>344.0264638260794</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40567,28 +40775,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05833062867040802</v>
+        <v>0.06075970369431114</v>
       </c>
       <c r="J10" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K10" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01389932906713742</v>
+        <v>0.01521589657946398</v>
       </c>
       <c r="M10" t="n">
-        <v>2.923434385894742</v>
+        <v>2.919029140408445</v>
       </c>
       <c r="N10" t="n">
-        <v>13.20530307487388</v>
+        <v>13.16207695399756</v>
       </c>
       <c r="O10" t="n">
-        <v>3.633910163291585</v>
+        <v>3.627957683600728</v>
       </c>
       <c r="P10" t="n">
-        <v>348.9351723543862</v>
+        <v>348.9089480502562</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40645,28 +40853,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01632416179054414</v>
+        <v>0.01838118508136572</v>
       </c>
       <c r="J11" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K11" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001160014805233978</v>
+        <v>0.001486123575025311</v>
       </c>
       <c r="M11" t="n">
-        <v>2.731496835510873</v>
+        <v>2.727238548270717</v>
       </c>
       <c r="N11" t="n">
-        <v>12.55225663182004</v>
+        <v>12.50534985905349</v>
       </c>
       <c r="O11" t="n">
-        <v>3.54291640203661</v>
+        <v>3.536290409320689</v>
       </c>
       <c r="P11" t="n">
-        <v>357.3722561347764</v>
+        <v>357.3500503368725</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40704,7 +40912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L755"/>
+  <dimension ref="A1:L759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87517,6 +87725,254 @@
         </is>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>-39.857631592737754,176.9856354989393</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>-39.85800272253935,176.98487830192443</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>-39.85843311674196,176.9841609893261</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-39.85898099177032,176.98359472348753</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-39.85951182590797,176.9830159222758</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>-39.86003437761515,176.9824138876503</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>-39.86056192759657,176.98181298106113</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>-39.86118355496259,176.98139686084602</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>-39.86185811234983,176.98113043683173</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>-39.86250183874252,176.98080753792664</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>-39.857627362562745,176.98563173700788</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>-39.858000867191734,176.9848766519575</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>-39.858425839824925,176.98415373396293</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>-39.85897712007509,176.98358903622886</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-39.85950852925435,176.9830095135846</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>-39.86003214002691,176.98240936988674</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>-39.86055772067442,176.98180414010076</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>-39.861184373594675,176.9813988081682</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>-39.86185887882074,176.98113254940006</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>-39.86250119617149,176.98080573681673</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>-39.857629292116265,176.98563345297654</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>-39.85800257411153,176.98487816992704</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>-39.858425768482604,176.98415366283191</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>-39.85897664355871,176.9835883362586</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>-39.859507330471104,176.98300718315156</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>-39.860030437514006,176.98240593245816</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>-39.86055913873814,176.98180712019962</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>-39.861186269374144,176.98140331775662</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>-39.86185922373262,176.98113350005582</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>-39.86250070479362,176.98080435949743</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>-39.857630850601794,176.98563483895128</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>-39.858003464678376,176.9848789619112</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>-39.85842334284347,176.98415124437787</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>-39.858974797057776,176.98358562387395</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>-39.859507530268324,176.98300757155707</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>-39.86003121580564,176.98240750385406</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>-39.860560556801786,176.98181010029862</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>-39.86118609703056,176.981402907794</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>-39.86185811234983,176.98113043683173</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>-39.86249896607178,176.9807994859061</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L759"/>
+  <dimension ref="A1:L764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32324,6 +32324,216 @@
         <v>359.27</v>
       </c>
       <c r="L759" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="C760" t="n">
+        <v>329.91</v>
+      </c>
+      <c r="D760" t="n">
+        <v>335.6</v>
+      </c>
+      <c r="E760" t="n">
+        <v>353.06</v>
+      </c>
+      <c r="F760" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="G760" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="H760" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="I760" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="J760" t="n">
+        <v>352.25</v>
+      </c>
+      <c r="K760" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="C761" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D761" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="E761" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="F761" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="G761" t="n">
+        <v>339.6</v>
+      </c>
+      <c r="H761" t="n">
+        <v>329.66</v>
+      </c>
+      <c r="I761" t="n">
+        <v>338.06</v>
+      </c>
+      <c r="J761" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="K761" t="n">
+        <v>358.84</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>328.78</v>
+      </c>
+      <c r="C762" t="n">
+        <v>329.98</v>
+      </c>
+      <c r="D762" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="E762" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="F762" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="G762" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="H762" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="I762" t="n">
+        <v>337.83</v>
+      </c>
+      <c r="J762" t="n">
+        <v>350.86</v>
+      </c>
+      <c r="K762" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>328.84</v>
+      </c>
+      <c r="C763" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="D763" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="E763" t="n">
+        <v>351.45</v>
+      </c>
+      <c r="F763" t="n">
+        <v>345.96</v>
+      </c>
+      <c r="G763" t="n">
+        <v>340.2</v>
+      </c>
+      <c r="H763" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="I763" t="n">
+        <v>337.29</v>
+      </c>
+      <c r="J763" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="K763" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="C764" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="D764" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="E764" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="F764" t="n">
+        <v>345.87</v>
+      </c>
+      <c r="G764" t="n">
+        <v>339.88</v>
+      </c>
+      <c r="H764" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="I764" t="n">
+        <v>337.22</v>
+      </c>
+      <c r="J764" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="K764" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="L764" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32340,7 +32550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B764"/>
+  <dimension ref="A1:B769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39983,6 +40193,56 @@
       </c>
       <c r="B764" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -40151,28 +40411,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4401836375475784</v>
+        <v>-0.4421318799360234</v>
       </c>
       <c r="J2" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K2" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1246937783485814</v>
+        <v>0.1273052723623058</v>
       </c>
       <c r="M2" t="n">
-        <v>7.123572498176651</v>
+        <v>7.086610477764648</v>
       </c>
       <c r="N2" t="n">
-        <v>74.92602105369974</v>
+        <v>74.44948261129038</v>
       </c>
       <c r="O2" t="n">
-        <v>8.655981807611413</v>
+        <v>8.62841136080625</v>
       </c>
       <c r="P2" t="n">
-        <v>342.436637966387</v>
+        <v>342.4577211203346</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -40229,28 +40489,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1985965081224934</v>
+        <v>-0.2022691548717381</v>
       </c>
       <c r="J3" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K3" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1012893096785074</v>
+        <v>0.1058517953078993</v>
       </c>
       <c r="M3" t="n">
-        <v>3.682053402299097</v>
+        <v>3.676346464477627</v>
       </c>
       <c r="N3" t="n">
-        <v>19.27743120873906</v>
+        <v>19.20050541475755</v>
       </c>
       <c r="O3" t="n">
-        <v>4.390607157186698</v>
+        <v>4.381838131966715</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0552607223181</v>
+        <v>338.0950017025783</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -40307,28 +40567,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1486592826059505</v>
+        <v>-0.152966833903609</v>
       </c>
       <c r="J4" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K4" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03195936985671766</v>
+        <v>0.03420677609585487</v>
       </c>
       <c r="M4" t="n">
-        <v>5.023673525044476</v>
+        <v>5.012999242121557</v>
       </c>
       <c r="N4" t="n">
-        <v>36.87475068046071</v>
+        <v>36.703596774808</v>
       </c>
       <c r="O4" t="n">
-        <v>6.072458372064869</v>
+        <v>6.058349344071205</v>
       </c>
       <c r="P4" t="n">
-        <v>341.9784321436476</v>
+        <v>342.025052751196</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40385,28 +40645,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05023217489140925</v>
+        <v>-0.05412193158141455</v>
       </c>
       <c r="J5" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K5" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007132501544959813</v>
+        <v>0.008369738588604125</v>
       </c>
       <c r="M5" t="n">
-        <v>3.444857454639962</v>
+        <v>3.440506744460263</v>
       </c>
       <c r="N5" t="n">
-        <v>19.34920088170597</v>
+        <v>19.28086500644419</v>
       </c>
       <c r="O5" t="n">
-        <v>4.398772656287885</v>
+        <v>4.390998178824969</v>
       </c>
       <c r="P5" t="n">
-        <v>356.266597113566</v>
+        <v>356.3086973840478</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40463,28 +40723,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1912012230144396</v>
+        <v>-0.188802179460472</v>
       </c>
       <c r="J6" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K6" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06307458373127206</v>
+        <v>0.06242758166857398</v>
       </c>
       <c r="M6" t="n">
-        <v>4.331505688486628</v>
+        <v>4.316680662355119</v>
       </c>
       <c r="N6" t="n">
-        <v>29.91449036743143</v>
+        <v>29.74297309926179</v>
       </c>
       <c r="O6" t="n">
-        <v>5.469414078987934</v>
+        <v>5.453711864341733</v>
       </c>
       <c r="P6" t="n">
-        <v>349.9143005269853</v>
+        <v>349.8883512334858</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40541,28 +40801,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2604644320167772</v>
+        <v>-0.2567759026903871</v>
       </c>
       <c r="J7" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K7" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1108787485879021</v>
+        <v>0.1093960439333685</v>
       </c>
       <c r="M7" t="n">
-        <v>4.269984226893748</v>
+        <v>4.260356599838262</v>
       </c>
       <c r="N7" t="n">
-        <v>29.96809775132403</v>
+        <v>29.82178210540556</v>
       </c>
       <c r="O7" t="n">
-        <v>5.474312536869267</v>
+        <v>5.460932347631268</v>
       </c>
       <c r="P7" t="n">
-        <v>344.1717801723373</v>
+        <v>344.1318674386579</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40619,28 +40879,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1464670536011987</v>
+        <v>-0.1565344308202302</v>
       </c>
       <c r="J8" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K8" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04244779846559743</v>
+        <v>0.04824619719879064</v>
       </c>
       <c r="M8" t="n">
-        <v>4.046810934445029</v>
+        <v>4.064066171534437</v>
       </c>
       <c r="N8" t="n">
-        <v>26.65856868098542</v>
+        <v>26.85488830745631</v>
       </c>
       <c r="O8" t="n">
-        <v>5.163193651315571</v>
+        <v>5.182170231423926</v>
       </c>
       <c r="P8" t="n">
-        <v>341.1138693652686</v>
+        <v>341.2228080360375</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40697,28 +40957,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02148138318597408</v>
+        <v>0.0124927780436101</v>
       </c>
       <c r="J9" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K9" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001223046209241185</v>
+        <v>0.0004143042643528494</v>
       </c>
       <c r="M9" t="n">
-        <v>3.488461957397977</v>
+        <v>3.49746986929982</v>
       </c>
       <c r="N9" t="n">
-        <v>20.75868220875254</v>
+        <v>20.91995460125134</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5561696861237</v>
+        <v>4.573833687537332</v>
       </c>
       <c r="P9" t="n">
-        <v>344.0264638260794</v>
+        <v>344.1237335834428</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40775,28 +41035,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06075970369431114</v>
+        <v>0.06148441345260029</v>
       </c>
       <c r="J10" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K10" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01521589657946398</v>
+        <v>0.0158025591337706</v>
       </c>
       <c r="M10" t="n">
-        <v>2.919029140408445</v>
+        <v>2.903481159327719</v>
       </c>
       <c r="N10" t="n">
-        <v>13.16207695399756</v>
+        <v>13.08057804509031</v>
       </c>
       <c r="O10" t="n">
-        <v>3.627957683600728</v>
+        <v>3.616708178038465</v>
       </c>
       <c r="P10" t="n">
-        <v>348.9089480502562</v>
+        <v>348.9011149864839</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40853,28 +41113,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01838118508136572</v>
+        <v>0.01937206665508305</v>
       </c>
       <c r="J11" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K11" t="n">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001486123575025311</v>
+        <v>0.001674686080828325</v>
       </c>
       <c r="M11" t="n">
-        <v>2.727238548270717</v>
+        <v>2.71439843439817</v>
       </c>
       <c r="N11" t="n">
-        <v>12.50534985905349</v>
+        <v>12.42889853217256</v>
       </c>
       <c r="O11" t="n">
-        <v>3.536290409320689</v>
+        <v>3.525464300226647</v>
       </c>
       <c r="P11" t="n">
-        <v>357.3500503368725</v>
+        <v>357.3393371122287</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40912,7 +41172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L759"/>
+  <dimension ref="A1:L764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87973,6 +88233,316 @@
         </is>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>-39.85763077638819,176.9856347729525</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>-39.85800532002596,176.98488061187825</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>-39.85842441297838,176.98415231134288</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>-39.858974141847746,176.98358466141494</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>-39.85950877900084,176.98300999909148</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>-39.86003214002691,176.98240936988674</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>-39.860561265833574,176.98181159034817</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>-39.861185321484434,176.98140106296236</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>-39.86185661773144,176.98112631732363</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>-39.862499419651414,176.98080075727773</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>-39.85762684306756,176.98563127501635</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>-39.85800524581205,176.98488054587955</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>-39.85842084586196,176.98414875479304</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>-39.85896979363552,176.98357827418724</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>-39.85950378407042,176.98300028895437</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>-39.86003102123273,176.98240711100507</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>-39.860561029489645,176.981811093665</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>-39.86118256398685,176.98139450356132</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>-39.86185324525859,176.98111702202385</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>-39.86249734074466,176.98079493015794</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>-39.85762439401879,176.98562909705632</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>-39.85800583952326,176.98488107386905</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>-39.85841906230368,176.98414697651825</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>-39.85896776844063,176.98357529931437</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>-39.85950103685829,176.98299494837957</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>-39.860033550680384,176.98241221804201</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>-39.86056173852145,176.98181258371454</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>-39.86118157301104,176.9813921462767</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>-39.86185129075691,176.98111163497552</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>-39.86249681156835,176.98079344689114</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>-39.857624839300385,176.98562949304903</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>-39.85800658166229,176.9848817338559</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>-39.858414995790696,176.98414292205206</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>-39.858964551954486,176.9835705745166</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>-39.85949933858157,176.9829916469335</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>-39.86003393982617,176.98241300374005</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>-39.86056032045786,176.98180960361546</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>-39.86117924637201,176.98138661178263</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>-39.86184994943207,176.98110793798176</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>-39.862495072846045,176.98078857330034</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>-39.85762632357236,176.98563081302478</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>-39.858004058389604,176.98487948990064</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>-39.85841114330457,176.9841390809793</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>-39.858962169372,176.9835670746667</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>-39.859498889037724,176.98299077302136</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>-39.86003238324302,176.982409860948</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>-39.86055838243749,176.98180553081355</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>-39.86117894477064,176.98138589434822</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>-39.86184994943207,176.98110793798176</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>-39.86249344751846,176.98078401755268</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L764"/>
+  <dimension ref="A1:L769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32534,6 +32534,216 @@
         <v>357.81</v>
       </c>
       <c r="L764" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="C765" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="D765" t="n">
+        <v>333.15</v>
+      </c>
+      <c r="E765" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="F765" t="n">
+        <v>345.05</v>
+      </c>
+      <c r="G765" t="n">
+        <v>338.96</v>
+      </c>
+      <c r="H765" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="I765" t="n">
+        <v>337.14</v>
+      </c>
+      <c r="J765" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="K765" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="C766" t="n">
+        <v>330.09</v>
+      </c>
+      <c r="D766" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="E766" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="F766" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="G766" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="H766" t="n">
+        <v>328.67</v>
+      </c>
+      <c r="I766" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="J766" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="K766" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>329.69</v>
+      </c>
+      <c r="C767" t="n">
+        <v>330.11</v>
+      </c>
+      <c r="D767" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="E767" t="n">
+        <v>350.21</v>
+      </c>
+      <c r="F767" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="G767" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="H767" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="I767" t="n">
+        <v>337.07</v>
+      </c>
+      <c r="J767" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="K767" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="C768" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="D768" t="n">
+        <v>332.84</v>
+      </c>
+      <c r="E768" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="F768" t="n">
+        <v>344.97</v>
+      </c>
+      <c r="G768" t="n">
+        <v>338.83</v>
+      </c>
+      <c r="H768" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="I768" t="n">
+        <v>337.15</v>
+      </c>
+      <c r="J768" t="n">
+        <v>349.92</v>
+      </c>
+      <c r="K768" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="C769" t="n">
+        <v>330.29</v>
+      </c>
+      <c r="D769" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="E769" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="F769" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="G769" t="n">
+        <v>338.78</v>
+      </c>
+      <c r="H769" t="n">
+        <v>328.89</v>
+      </c>
+      <c r="I769" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="J769" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="K769" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="L769" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32550,7 +32760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B769"/>
+  <dimension ref="A1:B774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40243,6 +40453,56 @@
       </c>
       <c r="B769" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -40411,28 +40671,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4421318799360234</v>
+        <v>-0.4434253064906991</v>
       </c>
       <c r="J2" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K2" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1273052723623058</v>
+        <v>0.1296204131520763</v>
       </c>
       <c r="M2" t="n">
-        <v>7.086610477764648</v>
+        <v>7.046825614264694</v>
       </c>
       <c r="N2" t="n">
-        <v>74.44948261129038</v>
+        <v>73.97120103278321</v>
       </c>
       <c r="O2" t="n">
-        <v>8.62841136080625</v>
+        <v>8.600651198181636</v>
       </c>
       <c r="P2" t="n">
-        <v>342.4577211203346</v>
+        <v>342.4717722543533</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -40489,28 +40749,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2022691548717381</v>
+        <v>-0.2055877333246658</v>
       </c>
       <c r="J3" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K3" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1058517953078993</v>
+        <v>0.110217724067979</v>
       </c>
       <c r="M3" t="n">
-        <v>3.676346464477627</v>
+        <v>3.66895565596535</v>
       </c>
       <c r="N3" t="n">
-        <v>19.20050541475755</v>
+        <v>19.11670917595562</v>
       </c>
       <c r="O3" t="n">
-        <v>4.381838131966715</v>
+        <v>4.372265908651443</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0950017025783</v>
+        <v>338.1310548877145</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -40567,28 +40827,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.152966833903609</v>
+        <v>-0.1594363906038511</v>
       </c>
       <c r="J4" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K4" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03420677609585487</v>
+        <v>0.03743382660380568</v>
       </c>
       <c r="M4" t="n">
-        <v>5.012999242121557</v>
+        <v>5.013997931895183</v>
       </c>
       <c r="N4" t="n">
-        <v>36.703596774808</v>
+        <v>36.62078961137906</v>
       </c>
       <c r="O4" t="n">
-        <v>6.058349344071205</v>
+        <v>6.051511349355552</v>
       </c>
       <c r="P4" t="n">
-        <v>342.025052751196</v>
+        <v>342.0953443274147</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40645,28 +40905,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05412193158141455</v>
+        <v>-0.06016904455432336</v>
       </c>
       <c r="J5" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K5" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008369738588604125</v>
+        <v>0.01040447431053038</v>
       </c>
       <c r="M5" t="n">
-        <v>3.440506744460263</v>
+        <v>3.446526352580388</v>
       </c>
       <c r="N5" t="n">
-        <v>19.28086500644419</v>
+        <v>19.29168829373627</v>
       </c>
       <c r="O5" t="n">
-        <v>4.390998178824969</v>
+        <v>4.392230446337745</v>
       </c>
       <c r="P5" t="n">
-        <v>356.3086973840478</v>
+        <v>356.3743985809351</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40723,28 +40983,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.188802179460472</v>
+        <v>-0.1884969913298101</v>
       </c>
       <c r="J6" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K6" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06242758166857398</v>
+        <v>0.06311443985142107</v>
       </c>
       <c r="M6" t="n">
-        <v>4.316680662355119</v>
+        <v>4.290282692341744</v>
       </c>
       <c r="N6" t="n">
-        <v>29.74297309926179</v>
+        <v>29.54970050151995</v>
       </c>
       <c r="O6" t="n">
-        <v>5.453711864341733</v>
+        <v>5.435963622166722</v>
       </c>
       <c r="P6" t="n">
-        <v>349.8883512334858</v>
+        <v>349.8850362416262</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40801,28 +41061,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2567759026903871</v>
+        <v>-0.2545285455018071</v>
       </c>
       <c r="J7" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K7" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1093960439333685</v>
+        <v>0.1090754390838208</v>
       </c>
       <c r="M7" t="n">
-        <v>4.260356599838262</v>
+        <v>4.243809379153953</v>
       </c>
       <c r="N7" t="n">
-        <v>29.82178210540556</v>
+        <v>29.64649653857377</v>
       </c>
       <c r="O7" t="n">
-        <v>5.460932347631268</v>
+        <v>5.444859643606415</v>
       </c>
       <c r="P7" t="n">
-        <v>344.1318674386579</v>
+        <v>344.1074515052604</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40879,28 +41139,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1565344308202302</v>
+        <v>-0.1673078769216929</v>
       </c>
       <c r="J8" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K8" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04824619719879064</v>
+        <v>0.05467976270912966</v>
       </c>
       <c r="M8" t="n">
-        <v>4.064066171534437</v>
+        <v>4.085820074475818</v>
       </c>
       <c r="N8" t="n">
-        <v>26.85488830745631</v>
+        <v>27.11262300991381</v>
       </c>
       <c r="O8" t="n">
-        <v>5.182170231423926</v>
+        <v>5.206978299351151</v>
       </c>
       <c r="P8" t="n">
-        <v>341.2228080360375</v>
+        <v>341.3398562246582</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40957,28 +41217,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0124927780436101</v>
+        <v>0.002762716850989646</v>
       </c>
       <c r="J9" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K9" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004143042643528494</v>
+        <v>2.023085740276986e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.49746986929982</v>
+        <v>3.509397834483635</v>
       </c>
       <c r="N9" t="n">
-        <v>20.91995460125134</v>
+        <v>21.1366474199094</v>
       </c>
       <c r="O9" t="n">
-        <v>4.573833687537332</v>
+        <v>4.597460975354701</v>
       </c>
       <c r="P9" t="n">
-        <v>344.1237335834428</v>
+        <v>344.2294476626356</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -41035,28 +41295,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06148441345260029</v>
+        <v>0.06055204544107595</v>
       </c>
       <c r="J10" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K10" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0158025591337706</v>
+        <v>0.01555713848914109</v>
       </c>
       <c r="M10" t="n">
-        <v>2.903481159327719</v>
+        <v>2.88942476038461</v>
       </c>
       <c r="N10" t="n">
-        <v>13.08057804509031</v>
+        <v>12.99884776355194</v>
       </c>
       <c r="O10" t="n">
-        <v>3.616708178038465</v>
+        <v>3.605391485477262</v>
       </c>
       <c r="P10" t="n">
-        <v>348.9011149864839</v>
+        <v>348.9112467016748</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -41113,28 +41373,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01937206665508305</v>
+        <v>0.01862434855507209</v>
       </c>
       <c r="J11" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="K11" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001674686080828325</v>
+        <v>0.001571059760502425</v>
       </c>
       <c r="M11" t="n">
-        <v>2.71439843439817</v>
+        <v>2.700355642643952</v>
       </c>
       <c r="N11" t="n">
-        <v>12.42889853217256</v>
+        <v>12.35017360200824</v>
       </c>
       <c r="O11" t="n">
-        <v>3.525464300226647</v>
+        <v>3.514281377751109</v>
       </c>
       <c r="P11" t="n">
-        <v>357.3393371122287</v>
+        <v>357.3474593069619</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -41172,7 +41432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L764"/>
+  <dimension ref="A1:L769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88543,6 +88803,316 @@
         </is>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>-39.85762758520353,176.98563193500425</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>-39.85800457788693,176.98487995189143</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>-39.85840693410656,176.98413488425217</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>-39.858957999852386,176.9835609499299</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>-39.85949479319338,176.98298281071104</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>-39.860027908066044,176.98240082542168</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>-39.860556775298555,176.98180215336825</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>-39.86117860008335,176.9813850744232</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>-39.86184810990068,176.98110286781906</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>-39.86249148200577,176.98077850827667</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>-39.85762944054347,176.98563358497412</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>-39.85800665587619,176.98488179985458</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>-39.85840614934083,176.98413410181155</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>-39.858957999852386,176.9835609499299</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>-39.85949489309203,176.98298300491373</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>-39.860027470276954,176.98239994151155</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>-39.8605563498794,176.98180125933862</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>-39.861177781451005,176.98138312710137</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>-39.86184803325354,176.9811026565623</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>-39.862490801635936,176.98077660121967</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>-39.857631147456175,176.9856351029465</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>-39.858006804304,176.98488193185196</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>-39.8584059353138,176.98413388841868</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>-39.85895716594841,176.98355972498265</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>-39.85949469329473,176.9829826165084</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>-39.86002819992544,176.98240141469512</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>-39.860556255341805,176.98180106066536</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>-39.86117829848197,176.98138435698885</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>-39.861846806899116,176.981099276454</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>-39.86249114182086,176.98077755474816</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>-39.85763010846582,176.98563417896332</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>-39.85800658166229,176.9848817338559</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>-39.85840472249401,176.98413267919236</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>-39.85895698725471,176.98355946249396</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>-39.85949439359878,176.98298203390036</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>-39.86002727570403,176.9823995486626</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>-39.86055672802977,176.9818020540316</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>-39.861178643169254,176.98138517691385</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>-39.86184768834136,176.98110170590684</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>-39.86249201118229,176.98077999154324</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>-39.857630034252225,176.98563411296453</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>-39.85800814015422,176.9848831198283</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>-39.858403224304816,176.9841311854422</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>-39.858955974657015,176.98355797505803</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>-39.859494093902825,176.98298145129232</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>-39.86002703248785,176.98239905760144</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>-39.86055738979286,176.98180344474434</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>-39.86117713516228,176.981381589742</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>-39.86184650031051,176.98109843142694</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>-39.86249201118229,176.98077999154324</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
